--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationdispense-preparation.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationdispense-preparation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationdispense-preparation.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationdispense-preparation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationdispense-preparation.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationdispense-preparation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationdispense-preparation.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationdispense-preparation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -371,7 +371,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/Examples/ValueSet/JP_MedicationInstructionForDispenseJHSP0002_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationInstructionForDispenseJHSP0002_VS</t>
   </si>
   <si>
     <t>Extension.value[x]:valueString</t>
@@ -722,7 +722,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="82.23046875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="77.33203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationdispense-preparation.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationdispense-preparation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-release</t>
+    <t>1.2.0-b</t>
   </si>
   <si>
     <t>Name</t>
